--- a/utils/monday_sprint_sprint_2023-05.xlsx
+++ b/utils/monday_sprint_sprint_2023-05.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="112">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Abertura</t>
+    <t>Entrada Sprint</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,6 +51,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>SLA (15 dias)</t>
+  </si>
+  <si>
     <t>Semana</t>
   </si>
   <si>
@@ -60,27 +63,45 @@
     <t>16051</t>
   </si>
   <si>
-    <t>Sprint 2023-05</t>
+    <t>Setor não informado</t>
   </si>
   <si>
     <t>Melhoria</t>
   </si>
   <si>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Tratativa para movimentações dos setores de embalagem</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>19/09/2022</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Tratativa para movimentações dos setores de embalagem</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
     <t>Feito</t>
   </si>
   <si>
+    <t>Não</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
+    <t>Setembro</t>
+  </si>
+  <si>
     <t>18795</t>
   </si>
   <si>
@@ -90,15 +111,24 @@
     <t>Média</t>
   </si>
   <si>
+    <t>22/02/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
     <t>18682</t>
   </si>
   <si>
     <t>Ajustes romaneio impresso</t>
   </si>
   <si>
+    <t>23/02/2023</t>
+  </si>
+  <si>
     <t>18714</t>
   </si>
   <si>
@@ -126,6 +156,9 @@
     <t>Alteração de Geração do Comparativo Deposito_Carteira</t>
   </si>
   <si>
+    <t>24/02/2023</t>
+  </si>
+  <si>
     <t>18810</t>
   </si>
   <si>
@@ -156,6 +189,9 @@
     <t>Alterar a geração das tabelas de MPS contemplando cliente na chave</t>
   </si>
   <si>
+    <t>27/02/2023</t>
+  </si>
+  <si>
     <t>18863</t>
   </si>
   <si>
@@ -207,12 +243,21 @@
     <t>Bloqueio Orçamento</t>
   </si>
   <si>
+    <t>28/02/2023</t>
+  </si>
+  <si>
     <t>4135163299</t>
   </si>
   <si>
+    <t>13/03/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
+    <t>Março</t>
+  </si>
+  <si>
     <t>Dashboard de Change Log - Governança de TI</t>
   </si>
   <si>
@@ -258,7 +303,7 @@
     <t>Distribuição por Tipo</t>
   </si>
   <si>
-    <t>Cumprimento SLA</t>
+    <t>Cumprimento SLA (15 dias)</t>
   </si>
   <si>
     <t>Status Final</t>
@@ -276,10 +321,10 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>A fazer</t>
+  </si>
+  <si>
+    <t>Abertos</t>
   </si>
   <si>
     <t>Impedimento</t>
@@ -720,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -730,13 +775,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -779,1061 +826,1136 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="J24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>17</v>
+        <v>79</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1849,23 +1971,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -1873,16 +1995,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1893,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>18.17</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -1901,12 +2023,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K22">
         <v>24</v>
@@ -1914,7 +2036,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1922,7 +2044,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1953,12 +2075,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="B2">
         <v>24</v>
@@ -1972,7 +2094,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>18.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -1982,60 +2104,60 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N10">
         <v>24</v>
       </c>
       <c r="P10" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -2043,31 +2165,31 @@
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E11">
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11">
         <v>3</v>
       </c>
       <c r="J11" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="K11">
         <v>24</v>
       </c>
       <c r="M11" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -2075,25 +2197,31 @@
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H12">
         <v>18</v>
       </c>
+      <c r="J12" t="s">
+        <v>103</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
       <c r="M12" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q12">
         <v>22</v>
@@ -2101,13 +2229,13 @@
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2115,13 +2243,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2129,7 +2257,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2137,7 +2265,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2145,7 +2273,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2153,7 +2281,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -2164,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2172,142 +2300,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" s="2">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2023-05.xlsx
+++ b/utils/monday_sprint_sprint_2023-05.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="125">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>16051</t>
+    <t>3255934624</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>19/09/2022</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>11/03/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>18795</t>
+    <t>4030577373</t>
   </si>
   <si>
     <t>Incluir na Planilha do MPS data e hora.</t>
@@ -120,7 +120,7 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>18682</t>
+    <t>4037121230</t>
   </si>
   <si>
     <t>Ajustes romaneio impresso</t>
@@ -129,13 +129,16 @@
     <t>23/02/2023</t>
   </si>
   <si>
-    <t>18714</t>
+    <t>4037144122</t>
   </si>
   <si>
     <t>Relatório de Tempo Logístico</t>
   </si>
   <si>
-    <t>18723</t>
+    <t>05/03/2023</t>
+  </si>
+  <si>
+    <t>4037794120</t>
   </si>
   <si>
     <t>Indefinido</t>
@@ -144,13 +147,19 @@
     <t>Adicionar um campo de observação na programação.</t>
   </si>
   <si>
-    <t>18725</t>
+    <t>02/03/2023</t>
+  </si>
+  <si>
+    <t>4037939570</t>
   </si>
   <si>
     <t>Sistema ENDs | Movimentação + Relatório</t>
   </si>
   <si>
-    <t>18747</t>
+    <t>09/03/2023</t>
+  </si>
+  <si>
+    <t>4041214781</t>
   </si>
   <si>
     <t>Alteração de Geração do Comparativo Deposito_Carteira</t>
@@ -159,31 +168,34 @@
     <t>24/02/2023</t>
   </si>
   <si>
-    <t>18810</t>
+    <t>4041353751</t>
   </si>
   <si>
     <t>Alteração Fluxo Pré Produtivo</t>
   </si>
   <si>
-    <t>18808</t>
+    <t>4043935303</t>
   </si>
   <si>
     <t>Tipos de OTF - Atrelar valor e peso em carteira.</t>
   </si>
   <si>
-    <t>18819</t>
+    <t>4044104474</t>
   </si>
   <si>
     <t>Criação de base de dados de Roteiro de Produção a partir do agrupamento de etapas</t>
   </si>
   <si>
-    <t>18677</t>
+    <t>4044313115</t>
   </si>
   <si>
     <t>Enviar OC automático</t>
   </si>
   <si>
-    <t>18861</t>
+    <t>28/02/2023</t>
+  </si>
+  <si>
+    <t>4051028545</t>
   </si>
   <si>
     <t>Alterar a geração das tabelas de MPS contemplando cliente na chave</t>
@@ -192,7 +204,7 @@
     <t>27/02/2023</t>
   </si>
   <si>
-    <t>18863</t>
+    <t>4051102582</t>
   </si>
   <si>
     <t>Alterar o campo "numero de linha" na tabela de fluxo de produção</t>
@@ -207,10 +219,13 @@
     <t>Não definida</t>
   </si>
   <si>
+    <t>12/03/2023</t>
+  </si>
+  <si>
     <t>4053209260</t>
   </si>
   <si>
-    <t>16359</t>
+    <t>4053697115</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -219,33 +234,54 @@
     <t>Definir tema e menu Sistema de Logística Interna</t>
   </si>
   <si>
+    <t>4053736802</t>
+  </si>
+  <si>
     <t>Analise Sistema de Logística Interna.</t>
   </si>
   <si>
+    <t>06/03/2023</t>
+  </si>
+  <si>
+    <t>4053763296</t>
+  </si>
+  <si>
     <t>Criar Estrutura de Dados para locais/rota (Amarelo/Azul/Verde/Vermelho)</t>
   </si>
   <si>
+    <t>4053781540</t>
+  </si>
+  <si>
     <t>Criar estrutura de dados para operadores/rota</t>
   </si>
   <si>
+    <t>07/03/2023</t>
+  </si>
+  <si>
+    <t>4053800280</t>
+  </si>
+  <si>
     <t>Criar estrutura de coleta/entrega</t>
   </si>
   <si>
+    <t>4053816486</t>
+  </si>
+  <si>
     <t>Criar funcionalidade que permita unir contentores</t>
   </si>
   <si>
+    <t>4053840820</t>
+  </si>
+  <si>
     <t>Criar funcionalidade que permita esvaziar contentor</t>
   </si>
   <si>
-    <t>18776</t>
+    <t>4059032041</t>
   </si>
   <si>
     <t>Bloqueio Orçamento</t>
   </si>
   <si>
-    <t>28/02/2023</t>
-  </si>
-  <si>
     <t>4135163299</t>
   </si>
   <si>
@@ -264,7 +300,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-05</t>
+    <t>Set/2022</t>
   </si>
   <si>
     <t>Base</t>
@@ -319,6 +355,9 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
   </si>
   <si>
     <t>A fazer</t>
@@ -1003,7 +1042,7 @@
         <v>37</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1020,22 +1059,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
@@ -1050,7 +1089,7 @@
         <v>37</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1067,7 +1106,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1079,10 +1118,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
@@ -1097,7 +1136,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1114,7 +1153,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1126,10 +1165,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
@@ -1141,10 +1180,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1161,7 +1200,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1173,10 +1212,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>31</v>
@@ -1188,7 +1227,7 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>24</v>
@@ -1208,7 +1247,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1220,10 +1259,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -1235,7 +1274,7 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>24</v>
@@ -1255,7 +1294,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1267,10 +1306,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
@@ -1282,7 +1321,7 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>24</v>
@@ -1302,7 +1341,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1314,10 +1353,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -1329,10 +1368,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1349,22 +1388,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1376,7 +1415,7 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>24</v>
@@ -1396,22 +1435,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1423,7 +1462,7 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>24</v>
@@ -1443,25 +1482,25 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1470,10 +1509,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1490,25 +1529,25 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
@@ -1517,10 +1556,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1537,22 +1576,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>31</v>
@@ -1564,10 +1603,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1584,22 +1623,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>31</v>
@@ -1611,10 +1650,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1631,22 +1670,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>31</v>
@@ -1658,10 +1697,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1678,22 +1717,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>31</v>
@@ -1705,10 +1744,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1725,22 +1764,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -1752,10 +1791,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1772,22 +1811,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>31</v>
@@ -1799,7 +1838,7 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>24</v>
@@ -1819,22 +1858,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>31</v>
@@ -1846,7 +1885,7 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>24</v>
@@ -1866,7 +1905,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1878,10 +1917,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>31</v>
@@ -1893,10 +1932,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1913,25 +1952,25 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -1940,10 +1979,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -1952,10 +1991,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1971,23 +2010,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -1995,16 +2034,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2015,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>18.17</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2023,7 +2062,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2036,7 +2075,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2044,7 +2083,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2075,12 +2114,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B2">
         <v>24</v>
@@ -2094,7 +2133,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2104,25 +2143,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2139,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2157,15 +2196,15 @@
         <v>24</v>
       </c>
       <c r="P10" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -2183,21 +2222,21 @@
         <v>24</v>
       </c>
       <c r="M11" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -2209,13 +2248,13 @@
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2224,18 +2263,18 @@
         <v>33</v>
       </c>
       <c r="Q12">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2243,13 +2282,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2257,7 +2296,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2265,7 +2304,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2273,7 +2312,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2281,10 +2320,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2292,7 +2331,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2300,142 +2339,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
